--- a/results/Int All Data 0.8/Rando_fi_explain.xlsx
+++ b/results/Int All Data 0.8/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.001326152981118873</v>
+        <v>0.0004320904835064043</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0006794584208393195</v>
+        <v>-2.891213223724764e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.000470579073294024</v>
+        <v>8.750359428114639e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0001906728171425043</v>
+        <v>0.000413259068598455</v>
       </c>
       <c r="F3" t="n">
-        <v>7.784182166230113e-05</v>
+        <v>2.184394179897242e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.001403124029479299</v>
+        <v>-0.000246519047731898</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.001107077878770963</v>
+        <v>0.001240555115792845</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0005388699274915353</v>
+        <v>0.0001767500947217082</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.001822847622384223</v>
+        <v>0.0001965763342992299</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0001604569395771705</v>
+        <v>3.785215820984346e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.934512451308271e-05</v>
+        <v>5.61446705920399e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.000262576707832255</v>
+        <v>-0.0002041983469359532</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0007175940104648648</v>
+        <v>-0.0001380251242753971</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003978186404295714</v>
+        <v>0.0004637247739322493</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0001285815301637449</v>
+        <v>-0.0002796599719859028</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001792961693383833</v>
+        <v>0.001302792863029345</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0004611555378914223</v>
+        <v>0.0004562225133230925</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0004719321541170618</v>
+        <v>5.565702832686318e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0001994358021968001</v>
+        <v>0.0001010249785086714</v>
       </c>
       <c r="U3" t="n">
-        <v>-4.561845161344283e-05</v>
+        <v>0.000489186338256764</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0009636482498481147</v>
+        <v>0.0002510492535283115</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0005590975482415795</v>
+        <v>-0.0001186855873115</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0002701075172497269</v>
+        <v>0.001271722377645028</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.0002352802322260939</v>
+        <v>7.223229749978911e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.0007012343388898001</v>
+        <v>-0.0001692355676119173</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.001631428162028915</v>
+        <v>-0.000495606161578126</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.0002116616282107575</v>
+        <v>-0.0002562306057343844</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.001513924428138423</v>
+        <v>0.0001646843499183325</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0009252280682290982</v>
+        <v>0.002182369497100358</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.005973763062065904</v>
+        <v>0.004854284148391027</v>
       </c>
       <c r="AF3" t="n">
-        <v>-9.884964745087155e-05</v>
+        <v>-0.0007837524142030627</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4.177493110074205e-05</v>
+        <v>4.444464255533465e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0002232758748572861</v>
+        <v>0.0005112861733130214</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.0002583817964872448</v>
+        <v>0.0005191911533281468</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.002943490012443207</v>
+        <v>0.00191824557393026</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.007745419359569771</v>
+        <v>0.007235317747906539</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.000116097177539799</v>
+        <v>0.0003796252459522498</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.00118221271882038</v>
+        <v>0.0007553739320386822</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0001400982265947048</v>
+        <v>-0.001031226211700197</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.663045988701148e-05</v>
+        <v>0.001021962202830053</v>
       </c>
       <c r="AP3" t="n">
-        <v>-7.259399580452741e-05</v>
+        <v>-9.465884789605193e-05</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.0001085483350554728</v>
+        <v>0.0008512718486098237</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.005789104231543651</v>
+        <v>0.003441721743985895</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0002487117920679472</v>
+        <v>0.0003671173055660447</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0009508528307519617</v>
+        <v>-0.0003714506529030837</v>
       </c>
       <c r="AU3" t="n">
-        <v>-9.137130365893475e-05</v>
+        <v>-9.089990753186838e-05</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.0003926416124503229</v>
+        <v>-0.0002299581089829606</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0005815358986790942</v>
+        <v>0.0002542855635314821</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0001249307641270747</v>
+        <v>-0.0001232233839011099</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.0006590642828321025</v>
+        <v>-0.0004725476730646161</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.0005627787360906134</v>
+        <v>0.0003391033412180422</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.17766889886651e-05</v>
+        <v>-0.0007030626163166786</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.001622731014776786</v>
+        <v>2.162896096508209e-05</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0001320731588462987</v>
+        <v>-1.169305905379667e-06</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.0001327789972780858</v>
+        <v>4.852469888661281e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0001439313070117954</v>
+        <v>-0.0003782448947133543</v>
       </c>
       <c r="BF3" t="n">
-        <v>-5.792112141408175e-05</v>
+        <v>0.000449528484386579</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0001665082682001451</v>
+        <v>-0.0001299755401183644</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.0003132945095775397</v>
+        <v>6.299202011439075e-05</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.000643708745960707</v>
+        <v>0.001688897660295298</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0001059917624699902</v>
+        <v>0.001785424649795608</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.000336689811194969</v>
+        <v>0.0004600973402108655</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0002944870475861405</v>
+        <v>-0.0001462127492933296</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.001329514766435596</v>
+        <v>-2.449512540718234e-05</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.0003922413100842072</v>
+        <v>-0.0003861822752752852</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.0008985358306514023</v>
+        <v>3.40099042095943e-05</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.002494182877936466</v>
+        <v>-0.0004277267784246785</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.0006892178043947461</v>
+        <v>0.0003668918758687967</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0003045099066376888</v>
+        <v>-6.891476350557842e-06</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.000382624906785226</v>
+        <v>0.0001029885139444675</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.001270089643801567</v>
+        <v>-0.0009047447467932944</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0004671220916748365</v>
+        <v>-0.0001421546491607428</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-3.865263439196686e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.0003723218984555776</v>
+        <v>-0.0004366508502359323</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.00112704957862234</v>
+        <v>6.794839303526428e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-4.702703939935879e-05</v>
+        <v>0.0006548198912294534</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0005701918122245585</v>
+        <v>0.0002937178771013116</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.000472560761135069</v>
+        <v>0.0001773918782922113</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0001090492948350885</v>
+        <v>-0.0001356151701569075</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.000632252469687028</v>
+        <v>0.0004575043448736593</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0009643464976205274</v>
+        <v>-4.730736197303348e-05</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.000769819184248971</v>
+        <v>5.713016776039305e-05</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.001347670991372637</v>
+        <v>-0.0003989780228594919</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0001348255454325098</v>
+        <v>0.0004827573488688918</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0009818532090662246</v>
+        <v>-0.0005653776117722697</v>
       </c>
       <c r="CJ3" t="n">
-        <v>5.277044854881119e-06</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0001823512773967318</v>
+        <v>-0.0003361770821290443</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.0002734786908687015</v>
+        <v>-0.0002117036359122149</v>
       </c>
       <c r="CM3" t="n">
-        <v>-1.961987278852552e-05</v>
+        <v>-4.023283086426188e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.0001505849571312346</v>
+        <v>0.0002641491268773333</v>
       </c>
       <c r="CO3" t="n">
-        <v>-2.487165012237448e-05</v>
+        <v>6.977192164936198e-05</v>
       </c>
       <c r="CP3" t="n">
-        <v>-5.344735435595105e-06</v>
+        <v>-1.603420630678864e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0001384394190472615</v>
+        <v>0.0005584071049614803</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.001397833985122294</v>
+        <v>-0.001114237662946261</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.001190900204432977</v>
+        <v>-0.0004482122557400036</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.0004392606507816166</v>
+        <v>-0.0005381715781982155</v>
       </c>
       <c r="CU3" t="n">
-        <v>-5.465003134443536e-05</v>
+        <v>2.455795677799855e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0001316488532912818</v>
+        <v>-6.712166139568043e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.001122782128910347</v>
+        <v>-0.0004738096336734265</v>
       </c>
       <c r="CY3" t="n">
-        <v>-2.003402599554892e-05</v>
+        <v>-0.0002702767160309706</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-2.672367717797664e-05</v>
+        <v>1.179123650923097e-05</v>
       </c>
       <c r="DA3" t="n">
-        <v>7.112312187003257e-05</v>
+        <v>1.64994304215893e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>-8.089004885328599e-05</v>
+        <v>1.709695735619521e-05</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.001062831221329608</v>
+        <v>-0.0002815039677874653</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0.0001101403773751497</v>
+        <v>-0.0001136546169522101</v>
       </c>
       <c r="DE3" t="n">
-        <v>-4.801420609831575e-05</v>
+        <v>-0.0001528205542164951</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.0002153473385298921</v>
+        <v>-8.721520794144677e-05</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.0001671471664647972</v>
+        <v>0.000398417447748225</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.002283065018494433</v>
+        <v>-0.0002307467767219584</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.0005351539495196756</v>
+        <v>0.0006633396553510717</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.0004886581687745683</v>
+        <v>-0.0001426061820361191</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0006483891671358588</v>
+        <v>2.693919393732537e-06</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0.0007621711408901822</v>
+        <v>-0.0001136916533283327</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.00185767541156436</v>
+        <v>-0.0003217863852983349</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.001324983828157934</v>
+        <v>0.000793544677686483</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.001143773489788963</v>
+        <v>0.0001720470950936736</v>
       </c>
       <c r="DQ3" t="n">
-        <v>6.867245194008835e-07</v>
+        <v>-5.695042554377582e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.232862375718072e-06</v>
+        <v>6.558569929102532e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>-3.515944167027162e-05</v>
+        <v>-1.569573203344165e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.001432694111980337</v>
+        <v>0.0004543045761879495</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.002252911432448145</v>
+        <v>-0.0004232740865817907</v>
       </c>
       <c r="DV3" t="n">
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>1.068947087119243e-05</v>
+        <v>1.40862756209259e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.0008040478839618503</v>
+        <v>3.270162706195959e-06</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.001280194037029935</v>
+        <v>-0.001604092392054559</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-1.473477406680024e-05</v>
+        <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0002173646960435305</v>
+        <v>-0.0002623491775105047</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.001773132787531729</v>
+        <v>0.0008793971213853514</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.0005172048185652655</v>
+        <v>0.0006205585404467529</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0.0004309880406190026</v>
+        <v>-3.332480037503861e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>6.211023595589226e-06</v>
+        <v>-5.527915975677144e-06</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.000300372909704898</v>
+        <v>-2.31513083258217e-05</v>
       </c>
       <c r="EG3" t="n">
-        <v>-6.298971487846417e-05</v>
+        <v>0.000129011730394285</v>
       </c>
       <c r="EH3" t="n">
-        <v>5.744961307303509e-05</v>
+        <v>-0.0001310135931496948</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.0005997850011117967</v>
+        <v>-0.0001304267425732541</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-6.206213062676104e-05</v>
+        <v>-0.0001849426575473934</v>
       </c>
       <c r="EK3" t="n">
-        <v>-2.960711703690722e-05</v>
+        <v>-1.534342498197838e-05</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>-4.302889862817236e-07</v>
+        <v>2.137894174238486e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>-8.205061432955851e-05</v>
+        <v>-1.783164206049404e-05</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0001015499732763281</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0001726570750954392</v>
+        <v>-0.000109015895098894</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>1.068947087119243e-05</v>
+        <v>0</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.0004684243756407835</v>
+        <v>-1.603420630678531e-05</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.0002358866550114758</v>
+        <v>-0.0001571832922532723</v>
       </c>
       <c r="EV3" t="n">
-        <v>1.978005343745926e-05</v>
+        <v>-5.756148613291545e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.0001768461611934035</v>
+        <v>-0.0001434214375632248</v>
       </c>
       <c r="EX3" t="n">
-        <v>-1.625162685303661e-05</v>
+        <v>-0.0002486514271002571</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0001140320508147619</v>
+        <v>-0.0001136052308202051</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00395712825141819</v>
+        <v>0.002370660839104582</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008285726756554253</v>
+        <v>0.0006954066000382345</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001439031936543775</v>
+        <v>0.0005272020698154935</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006138315006420669</v>
+        <v>0.0005456033126732002</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000249245454641751</v>
+        <v>0.0003145189287537369</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002043094906656415</v>
+        <v>0.002335165409997163</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003571359103660471</v>
+        <v>0.002299788922241778</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00277097155144267</v>
+        <v>0.001465537194368677</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003924505582099052</v>
+        <v>0.002267472533927041</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005883572601791786</v>
+        <v>0.0001284422997826087</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002837105257188521</v>
+        <v>0.0001317715577149001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001505214136529987</v>
+        <v>0.0005100831608413342</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001531654901665493</v>
+        <v>0.001966612082691147</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001266033586693933</v>
+        <v>0.001093476380112305</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001564838887108166</v>
+        <v>0.0008374136747745978</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004395906415838259</v>
+        <v>0.001962651320217005</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002160455458105472</v>
+        <v>0.00169466721733313</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002634299320456985</v>
+        <v>0.00219597974400415</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0005122134566359496</v>
+        <v>0.0002632392300721336</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001617113905177033</v>
+        <v>0.0008851345306257254</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002352562812309407</v>
+        <v>0.001493194302461864</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002718088686418521</v>
+        <v>0.001853020765617321</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002322019871792425</v>
+        <v>0.002248935451778634</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0007625851701500292</v>
+        <v>0.0002760916915002588</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001729182614089412</v>
+        <v>0.0008221658308630631</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003297574114875569</v>
+        <v>0.002010349137887756</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0006417263209015705</v>
+        <v>0.0008522495888548654</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.004759535481322442</v>
+        <v>0.001477279439559604</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0058156513386284</v>
+        <v>0.005006478839406296</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.007423984690784803</v>
+        <v>0.006320477060852648</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.003493880512770964</v>
+        <v>0.002836410734365589</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0006765533127733519</v>
+        <v>0.0004705840037693512</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001031237086763692</v>
+        <v>0.001060038888777504</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001314497713471396</v>
+        <v>0.0009899008582375487</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004103160092139713</v>
+        <v>0.00451658748424055</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.009710412538334294</v>
+        <v>0.007198867349702859</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0003917093120576645</v>
+        <v>0.0004628347327476244</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.002972246233590459</v>
+        <v>0.002842254571965631</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0008395329641479225</v>
+        <v>0.004535088885878293</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.002985731355838714</v>
+        <v>0.002799101159179586</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0003331539062330774</v>
+        <v>0.0004760399500162628</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0006139231301207594</v>
+        <v>0.001818797544197194</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.004695737101419848</v>
+        <v>0.004168918630167852</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.002404628286209468</v>
+        <v>0.001225490991563768</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.002884398740873014</v>
+        <v>0.001175060797429866</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0009703246387327004</v>
+        <v>0.0005726485550714214</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0009682564593600328</v>
+        <v>0.0008591064121826539</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002181095075930042</v>
+        <v>0.002037872825607447</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0004596467168696829</v>
+        <v>0.0003842652365014673</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002101956757582307</v>
+        <v>0.002870454379695546</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.001548964176852112</v>
+        <v>0.000645305206100883</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.00180303523617451</v>
+        <v>0.002428987543114755</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.007370666514995566</v>
+        <v>0.008135394419998975</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0004837356234368129</v>
+        <v>9.322406197844965e-05</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0008934711192953285</v>
+        <v>0.0002840703632688654</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001198633652898552</v>
+        <v>0.001504668608008908</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.006060504664009978</v>
+        <v>0.00502003464661685</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.001010797845589751</v>
+        <v>0.0007261916454024192</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0005182549152093788</v>
+        <v>0.0003948221983028816</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.003975846070470436</v>
+        <v>0.004130387255497688</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001768760784926163</v>
+        <v>0.001828419656252535</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.001409812850859343</v>
+        <v>0.001221145233350249</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0004490228825497384</v>
+        <v>0.0003122050305422522</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.002246338649061975</v>
+        <v>0.0007414296145935904</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.002482073709415712</v>
+        <v>0.002316416342041795</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.003325160317818327</v>
+        <v>0.001408393910050901</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.008075890618365712</v>
+        <v>0.001413994599243897</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.002907544897509307</v>
+        <v>0.001333394164833277</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.002383977225243997</v>
+        <v>0.0009367697917601413</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001486628395267103</v>
+        <v>0.0006062745736599287</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.003253963912760584</v>
+        <v>0.002524674168329538</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.001056558772827672</v>
+        <v>0.0006218445999781742</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>0.0001632824929297844</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.001311588052905966</v>
+        <v>0.001244797474006035</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.002721585137136675</v>
+        <v>0.001741960655846012</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001530626807333335</v>
+        <v>0.002488436074336751</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001176653054404084</v>
+        <v>0.0004213479898169241</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001077489989478936</v>
+        <v>0.0003511070560389744</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.001837458056430176</v>
+        <v>0.000966275889353908</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.001566645654084884</v>
+        <v>0.001268626666807915</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.00213772819141909</v>
+        <v>0.002727974932199478</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001617289399404748</v>
+        <v>0.0005268592988926265</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004075979334404103</v>
+        <v>0.00134041066391853</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0004458652363395868</v>
+        <v>0.0007150384572605121</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.003356160809211894</v>
+        <v>0.002772920046552227</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.668748105629705e-05</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0004777757406629039</v>
+        <v>0.0006474087215918127</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.001144050474555729</v>
+        <v>0.0005051735931241825</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.0003156198298419</v>
+        <v>0.0003144526717434447</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0004113530576100283</v>
+        <v>0.0009856837484592249</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0002784252722524823</v>
+        <v>0.0001699078353597251</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.690153746749271e-05</v>
+        <v>5.070461240248867e-05</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0009116615253585123</v>
+        <v>0.001493366663738568</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.003425463457580705</v>
+        <v>0.002590801843680083</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.002426119081464578</v>
+        <v>0.001215613118711805</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.001231869854598642</v>
+        <v>0.0009959584710423502</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0002456221124600199</v>
+        <v>7.765907809844545e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0002907479253761614</v>
+        <v>0.0002807980370183833</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.00340404187998441</v>
+        <v>0.00124661026774498</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0004013483770703873</v>
+        <v>0.002256213950148168</v>
       </c>
       <c r="CZ4" t="n">
-        <v>8.450768733746708e-05</v>
+        <v>0.0001806823050700636</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0001448968438392026</v>
+        <v>6.895503548055281e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0007402008890193856</v>
+        <v>0.0002801362481947607</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.00406904385224416</v>
+        <v>0.001323614899458418</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0003052488493079889</v>
+        <v>0.0002955540727695351</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0002550667859168729</v>
+        <v>0.0005680861557812217</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.0009519975959071652</v>
+        <v>0.0007225807377153501</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0007485898194094636</v>
+        <v>0.001191966203926133</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.004940812255926727</v>
+        <v>0.002831396058152602</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.002376465804957576</v>
+        <v>0.001493354011336487</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.001571229238753753</v>
+        <v>0.0002285101701998729</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.001467078598918397</v>
+        <v>0.000235233896928077</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.001443360886211975</v>
+        <v>0.0007001265880978126</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.003617680432488172</v>
+        <v>0.001587793116880009</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.003107032916806002</v>
+        <v>0.001102761426058371</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.003028645766422971</v>
+        <v>0.00115304992933527</v>
       </c>
       <c r="DQ4" t="n">
-        <v>4.10525152247023e-05</v>
+        <v>0.0002401735191090373</v>
       </c>
       <c r="DR4" t="n">
-        <v>1.654776378946889e-05</v>
+        <v>0.0001893671192847478</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0001415238034645152</v>
+        <v>5.566885423305301e-05</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.002709366862001609</v>
+        <v>0.0006855175618934195</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.00441357106140069</v>
+        <v>0.002432540817203228</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>3.380307493499245e-05</v>
+        <v>0.0001127680454817454</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.002024791965756298</v>
+        <v>0.0004204297853628716</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.003889955257069499</v>
+        <v>0.005411365000245186</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.659544685907077e-05</v>
+        <v>0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.000447328288743598</v>
+        <v>0.0006577588293693689</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.003429271320785345</v>
+        <v>0.001370110630127906</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0007381799045699123</v>
+        <v>0.0007559385556487702</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.001252516054459014</v>
+        <v>0.0002285347102209247</v>
       </c>
       <c r="EE4" t="n">
-        <v>6.233716646465336e-05</v>
+        <v>1.748080519717172e-05</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0007862228060762361</v>
+        <v>0.0005410028579773527</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0008995288254495953</v>
+        <v>0.0003872568048574338</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0002011536338577409</v>
+        <v>0.0004986407816844413</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.001255266883082173</v>
+        <v>0.000506528014627356</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0004605549560978005</v>
+        <v>0.000580816701395196</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0002576860535637402</v>
+        <v>7.221254412696747e-05</v>
       </c>
       <c r="EL4" t="n">
         <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>2.418468302463515e-05</v>
+        <v>6.76061498699849e-05</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0001731705955971455</v>
+        <v>0.0003439275292723476</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0003211292118824282</v>
+        <v>0</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.001130793434243156</v>
+        <v>0.0003064952168586092</v>
       </c>
       <c r="ER4" t="n">
         <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>3.380307493499245e-05</v>
+        <v>0</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0008743470458085397</v>
+        <v>9.444046521075609e-05</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0007952571947033418</v>
+        <v>0.0005526273226204573</v>
       </c>
       <c r="EV4" t="n">
-        <v>6.688097512305176e-05</v>
+        <v>0.0001820254016842105</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0005949343568454932</v>
+        <v>0.0003912713167272435</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0003996102828531114</v>
+        <v>0.0006747558215479905</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0003421646418574921</v>
+        <v>0.0002986592077787678</v>
       </c>
     </row>
     <row r="5">
@@ -2614,433 +2614,433 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01229289150187061</v>
+        <v>-0.003313735970069509</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.002405130946018142</v>
+        <v>-0.001622187336473069</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.004543025120256517</v>
+        <v>-0.0004911591355599044</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.001375245579567797</v>
+        <v>-9.823182711196087e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0001563314226159407</v>
+        <v>-0.0007849293563579219</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.006092998396579319</v>
+        <v>-0.004911591355599177</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01113456464379947</v>
+        <v>-0.001496525921966874</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.008284339925173667</v>
+        <v>-0.003367183324425449</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01256012827365041</v>
+        <v>-0.004813359528487183</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001817210048102569</v>
+        <v>-0.0002672367717797996</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0005893909626719318</v>
+        <v>-0.0003206841261357729</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.004489577765900543</v>
+        <v>-0.001389631213254983</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.003143418467583536</v>
+        <v>-0.003634420096205271</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.001385542168674714</v>
+        <v>-0.00080171031533941</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00352752538749328</v>
+        <v>-0.002458578300374159</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.005500982318271142</v>
+        <v>-0.002259332023575622</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.006306787814003156</v>
+        <v>-0.001875977071391399</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.007696419027258106</v>
+        <v>-0.005718866916087672</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0002137894174237931</v>
+        <v>-0.0002672367717798108</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.002228915662650599</v>
+        <v>-0.0009823182711198087</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.007161945483698517</v>
+        <v>-0.003313735970069498</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.007856761090325981</v>
+        <v>-0.004168893639764836</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.004709576138147598</v>
+        <v>-0.0002616431187859591</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.00240513094601813</v>
+        <v>-0.0002763957987838572</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.005451630144307817</v>
+        <v>-0.001603420630678798</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.01036878674505608</v>
+        <v>-0.00349140177175612</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.001866404715127701</v>
+        <v>-0.0017103153393907</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.01403693931398417</v>
+        <v>-0.002946954813359504</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01155672823218997</v>
+        <v>-0.005893909626719029</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.000328947368421062</v>
+        <v>-0.003699843668577418</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.008230892570817706</v>
+        <v>-0.008658471405665447</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.00103143418467585</v>
+        <v>-0.0007367387033398454</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001626506024096375</v>
+        <v>-0.001178781925343764</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.00379476215927308</v>
+        <v>-0.0003869541182974001</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.001255886970172737</v>
+        <v>-0.004429390307451842</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.005329815303430086</v>
+        <v>-0.003915662650602369</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0008433734939758963</v>
+        <v>-0.0002211166390270858</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.003487229862475461</v>
+        <v>-0.006237721021610976</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.002013752455795692</v>
+        <v>-0.0135756280064137</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.004379947229551451</v>
+        <v>-0.002145473574045009</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.0009036144578313144</v>
+        <v>-0.00115122972265832</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.0008970976253297902</v>
+        <v>-0.002084418968212653</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0003663003663003206</v>
+        <v>-0.003908285565398672</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.003634420096205215</v>
+        <v>-0.002030999465526473</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.009032602886157082</v>
+        <v>-0.003094302554027495</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.001656867985034705</v>
+        <v>-0.0007228915662650159</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.002351683591662168</v>
+        <v>-0.002554027504911605</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.00662747194013893</v>
+        <v>-0.003848209513629086</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001080550098231847</v>
+        <v>-0.0009823182711197974</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.005718866916087617</v>
+        <v>-0.008202357563850671</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.004810261892036283</v>
+        <v>-0.0002672367717798108</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.003781925343811432</v>
+        <v>-0.007269155206286837</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.02175307322287542</v>
+        <v>-0.01747728487439872</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001229289150187018</v>
+        <v>-0.0001603420630678864</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.002458578300374104</v>
+        <v>-0.0003869541182974001</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.002701375245579596</v>
+        <v>-0.004567779960707241</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.01154462854088719</v>
+        <v>-0.01193516699410608</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.001175841795831056</v>
+        <v>-0.001412872841444268</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.001443078567610856</v>
+        <v>-0.0007367387033398564</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.008674698795180713</v>
+        <v>-0.001549973276322825</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.004115446285408842</v>
+        <v>-0.0004934210526315929</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.004115446285408819</v>
+        <v>-0.001255886970172693</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001046572475143948</v>
+        <v>-0.0009823182711198087</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.006413682522715081</v>
+        <v>-0.001667535174570145</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.006139489194499026</v>
+        <v>-0.006581532416502933</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.01015499732763223</v>
+        <v>-0.00192410475681456</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.02544094067343663</v>
+        <v>-0.004329235702832712</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.008284339925173656</v>
+        <v>-0.001360544217687099</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.006841261357562756</v>
+        <v>-0.002084446819882424</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.0008372579801151691</v>
+        <v>-0.0008844665561083432</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.01036878674505609</v>
+        <v>-0.007963655799037971</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.00308738880167454</v>
+        <v>-0.00167451596023025</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0.0004934210526315929</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.00406199893105289</v>
+        <v>-0.003474078033137373</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.007055050774986582</v>
+        <v>-0.004543025120256561</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.002825745682888592</v>
+        <v>-0.001459093277748891</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.0003647733194371949</v>
+        <v>-0.0003663003663003539</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.0002110817941952448</v>
+        <v>-0.0004810261892036371</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.004649919828968429</v>
+        <v>-0.002030999465526484</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.004489577765900532</v>
+        <v>-0.001686746987951771</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.006360235168359108</v>
+        <v>-0.004371316306483286</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.004649919828968408</v>
+        <v>-0.00115122972265832</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.01288081239978617</v>
+        <v>-0.00390165686798506</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0003693931398416783</v>
+        <v>-5.482456140351033e-05</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.01031533939070011</v>
+        <v>-0.008337787279529673</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.0008433734939758963</v>
+        <v>-0.001308215593929896</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.00326028861571348</v>
+        <v>-0.001302761855132939</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.0004216867469879259</v>
+        <v>-0.0008551576696953945</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.0009638554216867435</v>
+        <v>-0.0003126628452319036</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.0005344735435595327</v>
+        <v>-0.0001096491228070207</v>
       </c>
       <c r="CP5" t="n">
-        <v>-5.344735435595105e-05</v>
+        <v>-0.0001603420630678864</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.001496525921966829</v>
+        <v>-0.001068947087119188</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.01079636557990373</v>
+        <v>-0.008230892570817749</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.007749866381614068</v>
+        <v>-0.00363442009620526</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.003046499198289654</v>
+        <v>-0.003260288615713536</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.0005277044854881119</v>
+        <v>0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0.0008337675872850614</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.01058257616247992</v>
+        <v>-0.003901656867985037</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.0008895866038723721</v>
+        <v>-0.006360235168359174</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.0002672367717797664</v>
+        <v>-0.0003206841261357729</v>
       </c>
       <c r="DA5" t="n">
-        <v>-5.344735435595105e-05</v>
+        <v>-9.823182711197199e-05</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.00181721004810258</v>
+        <v>-0.0003614457831324968</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.01245323356493848</v>
+        <v>-0.00395510422234101</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.0009498680738786013</v>
+        <v>-0.0009379885356957107</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.0004810261892035927</v>
+        <v>-0.001360544217687099</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.002886157135221767</v>
+        <v>-0.001302761855132939</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.00160342063067872</v>
+        <v>-0.0008551576696953722</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.01493975903614459</v>
+        <v>-0.006987951807228876</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.005986103687867406</v>
+        <v>-0.000481927710843344</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.004939759036144575</v>
+        <v>-0.0005482456140351033</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.00403614457831325</v>
+        <v>-0.000374131480491735</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.004337349397590362</v>
+        <v>-0.001563314226159518</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.01054216867469878</v>
+        <v>-0.004756814537680398</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.009673971138428616</v>
+        <v>-0.0001473477406679358</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.008313253012048183</v>
+        <v>-0.001980198019802026</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-9.823182711199419e-05</v>
+        <v>-0.0007326007326007411</v>
       </c>
       <c r="DR5" t="n">
         <v>0</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.0004186289900576012</v>
+        <v>-0.0001569858712715755</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.007710843373493992</v>
+        <v>-0.0006626506024096201</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.01096385542168675</v>
+        <v>-0.006360235168359185</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0.0001603420630678864</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.006506024096385543</v>
+        <v>-0.0007849293563579329</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.01216867469879518</v>
+        <v>-0.0167290219134153</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0001473477406680024</v>
+        <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.00103143418467585</v>
+        <v>-0.001517530088958663</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.008975903614457836</v>
+        <v>-0.0006024096385541799</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.0002638522427440559</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.003975903614457832</v>
+        <v>-0.0006279434850863464</v>
       </c>
       <c r="EE5" t="n">
-        <v>-9.823182711199419e-05</v>
+        <v>-5.527915975677145e-05</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.002351683591662168</v>
+        <v>-0.001229289150187085</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.002030999465526417</v>
+        <v>-0.0002136752136752129</v>
       </c>
       <c r="EH5" t="n">
-        <v>-5.344735435595105e-05</v>
+        <v>-0.001229289150187085</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.003794762159273091</v>
+        <v>-0.0008349705304518285</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.001265060240963845</v>
+        <v>-0.001710315339390689</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.0005344735435595105</v>
+        <v>-0.0002136752136752129</v>
       </c>
       <c r="EL5" t="n">
         <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-5.341880341880323e-05</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0004275788348476195</v>
+        <v>-0.0008551576696953945</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.00326028861571348</v>
+        <v>-0.0008840864440078256</v>
       </c>
       <c r="ER5" t="n">
         <v>0</v>
@@ -3058,22 +3058,22 @@
         <v>0</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.002771084337349417</v>
+        <v>-0.0002672367717798108</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.002228915662650621</v>
+        <v>-0.001406982803543566</v>
       </c>
       <c r="EV5" t="n">
-        <v>-5.211047420531356e-05</v>
+        <v>-0.0005756148613291545</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.001746987951807222</v>
+        <v>-0.001175841795831134</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.0009638554216867435</v>
+        <v>-0.00203230849400734</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.001084337349397591</v>
+        <v>-0.000694815606627508</v>
       </c>
     </row>
     <row r="6">
@@ -3083,277 +3083,277 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0005854923564528437</v>
+        <v>-0.0008058376530358208</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.001229150795878306</v>
+        <v>-0.0002403846153846145</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0001105108055009935</v>
+        <v>-8.017103153394324e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0005742248392888643</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.001624876815970983</v>
+        <v>-8.291873963515718e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0005637614560807191</v>
+        <v>5.341880341880323e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.0002072968490878929</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001487724839704216</v>
+        <v>-4.51807228915635e-05</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.00029021558872305</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.0006314235577013689</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-4.006410256410242e-05</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.0004413030998851875</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0003226079089205886</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-3.924646781789388e-05</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.0002577025794684801</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.0001610844509431275</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.0003947579958767378</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.001703405721262879</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.0004053488288746049</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.0001859509255248193</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>8.856333985306772e-05</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.0006740752981354459</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.0006671899529042459</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-9.797898059900612e-05</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>4.008551576697161e-05</v>
+      </c>
+      <c r="AI6" t="n">
         <v>-4.51807228915635e-05</v>
       </c>
-      <c r="L6" t="n">
-        <v>-8.326672684688675e-18</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.001803848209513589</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.0002004275788348164</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-3.409487649458392e-07</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-3.908285565398517e-05</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.0001096424168131299</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.0003327090845740566</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.001303749926750233</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.0001355421686746905</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.763957987838572e-05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-0.000764456241853942</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-0.0009567258216570812</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-0.0002087689791246267</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.0002605614766759357</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.0005329873128711221</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.001052904525311496</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-0.0004053286845664167</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-0.000431501732523748</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-0.001013807468245337</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-0.0001306104055509433</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>6.818304699555966e-05</v>
+        <v>1.381978993919286e-05</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.004036797369184442</v>
+        <v>0.002659301331692965</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.000301448951903277</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>5.341880341880323e-05</v>
+        <v>0.0001520176893311215</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>-0.0004111842105263275</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0005290789309269183</v>
+        <v>-0.0003807908720966147</v>
       </c>
       <c r="AP6" t="n">
-        <v>-7.915567282321679e-05</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0005422219514978787</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.001485428094569879</v>
+        <v>0.001504447933019362</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0002474068352763842</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.0003816758399374564</v>
+        <v>-0.0008260477774105683</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>-0.0004590014690146999</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0007527866677828121</v>
+        <v>-8.017103153394324e-05</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.0004269103947722896</v>
+        <v>-0.0006325301204818889</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>-0.0001172485669619555</v>
       </c>
       <c r="AY6" t="n">
+        <v>-0.0003145383490778308</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0.0006165683578783415</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.001549337190450437</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.0001795339251743855</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.506024096386838e-05</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.0004282549760774607</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0.0006262278978388714</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-8.291873963515718e-05</v>
+      </c>
+      <c r="BL6" t="n">
         <v>-0.0001243781094527357</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>-0.0001841846758350058</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-0.0003327090845740566</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-0.0004259077346593116</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-0.0003126628452318813</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-7.915567282321679e-05</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>-0.001096848298357481</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>-0.0002334933401150652</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>-0.0004576027709356306</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>-0.002834999537616831</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>-0.0002086068904071287</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>-0.0001841846758349974</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>-0.000570073487030237</v>
-      </c>
       <c r="BM6" t="n">
-        <v>-0.002002103168606143</v>
+        <v>0</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.0004817023304334145</v>
+        <v>-0.0003162650602409362</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.0003468059555412795</v>
+        <v>-0.0004129055468341164</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.0004407051282051266</v>
+        <v>-9.39479950673977e-05</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-3.957783641160839e-05</v>
+        <v>-0.0003553479158949324</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0.0002782322382150121</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.0006022209979994003</v>
+        <v>-0.0005855052864519178</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.000180722891566254</v>
+        <v>-0.0002735799895778962</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0001237034176382046</v>
+        <v>-0.0006822287414347955</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.002737677554803225</v>
+        <v>-4.145936981757859e-05</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.000333711744687043</v>
+        <v>-8.74936602731552e-05</v>
       </c>
       <c r="CA6" t="n">
-        <v>-4.008551576696328e-05</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>0</v>
+        <v>2.455795677800132e-05</v>
       </c>
       <c r="CC6" t="n">
-        <v>0</v>
+        <v>-0.0004455309359360504</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.0007261114956743058</v>
+        <v>-0.0003529670401250767</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.001368448403668016</v>
+        <v>-0.0005100155703585352</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.001234083376940545</v>
+        <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0003512125424776108</v>
+        <v>-0.0002524309870258256</v>
       </c>
       <c r="CH6" t="n">
-        <v>-5.344021662163079e-05</v>
+        <v>0</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0002003205128205121</v>
+        <v>0</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0005343915069643684</v>
+        <v>-0.0007986070016805513</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.0003032432072743785</v>
+        <v>-0.000410710272117501</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.0001605403528051857</v>
+        <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0003206841261357313</v>
+        <v>0</v>
       </c>
       <c r="CO6" t="n">
         <v>0</v>
@@ -3365,13 +3365,13 @@
         <v>0</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.000740624056498504</v>
+        <v>-0.0006692479931418111</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.001203285659475647</v>
+        <v>-0.0001463566195709032</v>
       </c>
       <c r="CT6" t="n">
-        <v>-4.008551576696328e-05</v>
+        <v>-0.0005676961433891097</v>
       </c>
       <c r="CU6" t="n">
         <v>0</v>
@@ -3383,10 +3383,10 @@
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.0009868641231593036</v>
+        <v>-0.0001945941661382344</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-4.145936981757859e-05</v>
       </c>
       <c r="CZ6" t="n">
         <v>0</v>
@@ -3395,49 +3395,49 @@
         <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-7.849293563578775e-05</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.0001304411790991583</v>
+        <v>-0.0001534757450856017</v>
       </c>
       <c r="DD6" t="n">
-        <v>-3.683693516700614e-05</v>
+        <v>-7.849293563578775e-05</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.0001973942013004187</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0</v>
+        <v>-0.0004560530679933645</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.0001841846758349974</v>
+        <v>-0.0003176278694248052</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.00094887396809748</v>
+        <v>-0.000710862224721509</v>
       </c>
       <c r="DI6" t="n">
-        <v>2.670940170940161e-05</v>
+        <v>-0.0001202565473009315</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0.0002706335765295387</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.0006949318597695376</v>
+        <v>-8.012820512820484e-05</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.001202565473009065</v>
+        <v>-0.0001602564102564097</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.0009051216640502679</v>
+        <v>-8.012820512820484e-05</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.001136347619691919</v>
+        <v>5.527915975677145e-05</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.0003063476760706285</v>
+        <v>-0.0002754798960834553</v>
       </c>
       <c r="DQ6" t="n">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.002516157965879268</v>
+        <v>1.381978993919286e-05</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.001117938013198327</v>
+        <v>-0.0002936413300859197</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
@@ -3461,43 +3461,43 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.000340688335411321</v>
+        <v>-4.51807228915635e-05</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.0005552949287495445</v>
+        <v>-0.0005740401841878545</v>
       </c>
       <c r="DZ6" t="n">
         <v>0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.0004918713314797374</v>
+        <v>-0.000280448717948717</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.001326748648177259</v>
+        <v>1.227897838899927e-05</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>0.0001054216867469926</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.0001309320155909094</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.0004066265060240965</v>
+        <v>-0.0001105108055009685</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0002374670184696504</v>
+        <v>-4.008551576697162e-05</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-0.0001105108055009685</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.0003664015666717091</v>
+        <v>-0.0004527056420343789</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0</v>
+        <v>-0.000280448717948717</v>
       </c>
       <c r="EK6" t="n">
         <v>0</v>
@@ -3518,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-4.008551576697162e-05</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
@@ -3527,22 +3527,22 @@
         <v>0</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0004467011163440087</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.0003606781234483019</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.0002094249512267221</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0.0002946954813359326</v>
       </c>
       <c r="EY6" t="n">
-        <v>-3.92464678179022e-05</v>
+        <v>-0.0001602564102564097</v>
       </c>
     </row>
     <row r="7">
@@ -3552,73 +3552,73 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0001749002580953007</v>
+        <v>0.0001068947087119243</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0002911867603764384</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.000276831008243511</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0005664785049113386</v>
+        <v>0.0001336183858899054</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.0003546399968918868</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001769876339129506</v>
+        <v>0.0002939604489577752</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0002114059716302408</v>
+        <v>0.0001068947087119188</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5.287371358799753e-05</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.670940170940161e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.000131926121372028</v>
+        <v>2.763957987838572e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>8.22368421052655e-05</v>
+        <v>0.0001640056738695051</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001318605282890129</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0005674862032810756</v>
+        <v>0.001455613803638367</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.455795677798189e-05</v>
+        <v>0.0002485741284292853</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0001671818854364904</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5.776006180611692e-05</v>
+      </c>
+      <c r="W7" t="n">
         <v>-8.012820512820484e-05</v>
       </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
       <c r="X7" t="n">
-        <v>0.0002385077743758568</v>
+        <v>0.0007058332630078823</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -3627,314 +3627,314 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.000132898653677016</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
+        <v>0.0005077498663816071</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.001068947087119165</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.004097556637502536</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0001096491228070207</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.000227422849291925</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.0008548721603237941</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.006465909102542961</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.0002917229877602512</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.00136290753607694</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.0002137894174238486</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>2.616431187859036e-05</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.002807644889587135</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.012048192771455e-05</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.0001082719157594725</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.911591355599709e-05</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-2.616431187860147e-05</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.0006845781780568105</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.0004625456363293201</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-9.823182711196643e-05</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.0004912166034528376</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.002013773962767179</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>3.01204819277201e-05</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>5.34473543559455e-05</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.527915975677145e-05</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-5.482456140351033e-05</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>2.455795677800965e-05</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>5.482456140351033e-05</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
         <v>-8.291873963515717e-05</v>
       </c>
-      <c r="AD7" t="n">
-        <v>0.002606100616988771</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.003506380309306278</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-2.672367717796442e-05</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.001062050157444899</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.007637301682185188</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.0008403673307200155</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.0002422449717225827</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>2.616431187857926e-05</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0.004801633042056002</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>-0.0001055408970976224</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-0.0002667698396590201</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>2.672367717798108e-05</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.670940170940161e-05</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-3.0120481927709e-05</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0.0002487562189054715</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>8.017103153396544e-05</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0.0002487562189054715</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>-0.0001068947087119021</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0.0003981475344411178</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.000221021611001948</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>-0.0003714577201903823</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>-0.000264824775049044</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="n">
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>-0.0001065134294026104</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.0004494806768126136</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.0001870657402458675</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.0003515221749352537</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.0001136883182114024</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.0001964636542239773</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>8.291873963515717e-05</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.0003546399968918868</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.0001068661577747654</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>-0.0001563314226159462</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>-0.0001602564102564097</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.0002138700712176478</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>-0.0002930802155992285</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>-0.0002903720143732747</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>-0.0001065134294026104</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>-2.616431187859592e-05</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>9.036144578314365e-05</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0.0005315274996297359</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0.0001863174570958193</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.0005619322531157712</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0.0001302761855132839</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
         <v>5.344735435596215e-05</v>
       </c>
-      <c r="BS7" t="n">
-        <v>0.0001302761855132839</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0.0001105583195135429</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>7.849293563578774e-05</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>0.000120481927710836</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>0.0004198536781882589</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>-0.0001602564102564264</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>-2.220446049250313e-17</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>7.816571130797034e-05</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>-0.0001042209484106271</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>-2.45579567780152e-05</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>-0.0002872620567848927</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>-0.0001061892519676144</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>5.527915975677145e-05</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>5.197023747974817e-05</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>-7.816571130797034e-05</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>0.0002364770569544039</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>-0.0001533368619666242</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>-7.849293563580995e-05</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>-0.0001046572475144114</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>-0.0002123668844617232</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>-0.0002097618455082495</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>-2.45579567780152e-05</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>-7.816571130797034e-05</v>
-      </c>
       <c r="DZ7" t="n">
         <v>0</v>
       </c>
@@ -3942,10 +3942,10 @@
         <v>0</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.0003410279925367798</v>
+        <v>0.0004045187684713292</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0002136752136752129</v>
+        <v>0.0005076213871644086</v>
       </c>
       <c r="ED7" t="n">
         <v>0</v>
@@ -3996,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="ET7" t="n">
-        <v>-2.638522427440559e-05</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
         <v>0</v>
@@ -4021,163 +4021,163 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000280448717948717</v>
+        <v>0.0008916434970651893</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.638522427440559e-05</v>
+        <v>0.0003700657894736864</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.000732104295897515</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001105108055009685</v>
+        <v>0.0002003419260233785</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.93319835848849e-05</v>
+        <v>0.001010425234026235</v>
       </c>
       <c r="H8" t="n">
-        <v>9.594635818648556e-05</v>
+        <v>0.002177181890668406</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006599613549515105</v>
+        <v>0.00108821336426258</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.001581413821791988</v>
       </c>
       <c r="K8" t="n">
-        <v>3.924646781788554e-05</v>
+        <v>9.729708306912277e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.518072289158015e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0004611891438125737</v>
+        <v>9.219907598666533e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.0004820590944892955</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001067565624788575</v>
+        <v>0.0009082846195158311</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0004397325959001386</v>
+        <v>0.0001089605192832438</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003994690825047924</v>
+        <v>0.002485002192711963</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0002210216110019453</v>
+        <v>0.0004810261892036317</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003794040389435149</v>
+        <v>0.001187269684097977</v>
       </c>
       <c r="T8" t="n">
-        <v>3.908285565398517e-05</v>
+        <v>0.0002745612364880134</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.001125054275941498</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001172485669619555</v>
+        <v>0.001064827094507143</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0001187335092348252</v>
+        <v>8.017103153394324e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0005257176463108221</v>
+        <v>0.00122212819845198</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.367387033397065e-05</v>
+        <v>0.0002470514750807423</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.498001805406602e-17</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0001062262686366083</v>
+        <v>0.001125527752033806</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.004088855421686735</v>
+        <v>0.00463173594687401</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.005703331134564627</v>
+        <v>0.007541670895067992</v>
       </c>
       <c r="AF8" t="n">
+        <v>0.000340689681804146</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0004379078877043002</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.0009944438703905518</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.0008966935618513972</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.004639840500977713</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.01154199225356882</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.000721311597088764</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.001610058655675317</v>
+      </c>
+      <c r="AN8" t="n">
         <v>0.0006810897435897412</v>
       </c>
-      <c r="AG8" t="n">
-        <v>0.0001243781094527357</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.0001243781094527357</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.0001503127896200135</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.00633360619258036</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.01087374376605709</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0.0001187335092348252</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.001825209424106983</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.0005265999235090635</v>
-      </c>
       <c r="AO8" t="n">
-        <v>0.0004358959069512641</v>
+        <v>0.0016239299302473</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.33066907387547e-17</v>
+        <v>0.0001874118432320937</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>0.00266658051797049</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.009003979482016367</v>
+        <v>0.005640888777324771</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.000180722891566254</v>
+        <v>0.001251089810398032</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0001658374792703144</v>
+        <v>8.291873963515718e-05</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0002374670184696504</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>9.036144578314365e-05</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0001555704444018119</v>
+        <v>0.001804940902574098</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0001583113456464336</v>
+        <v>0.0001202565473009065</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0004360092794314319</v>
+        <v>0.0006304606289335741</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9.198550124717153e-05</v>
+        <v>0.0005276038363982493</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0001997707154640121</v>
+        <v>0.0002055921052631637</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.001720325079493934</v>
+        <v>0.002461269975681724</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
@@ -4186,196 +4186,196 @@
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0009312982882472815</v>
+        <v>0.0002004275788348414</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.002047465627129519</v>
+        <v>0.002645420792079184</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>0.0002804701311515778</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.001647899797570851</v>
+        <v>0.002036400502398403</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.0004936162560690432</v>
+        <v>0.003407459926154555</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0001918927163729711</v>
+        <v>0.0007928475033738225</v>
       </c>
       <c r="BL8" t="n">
         <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>3.924646781787722e-05</v>
+        <v>0.0003206412997300345</v>
       </c>
       <c r="BN8" t="n">
-        <v>-3.908285565398517e-05</v>
+        <v>0.0002004061656319722</v>
       </c>
       <c r="BO8" t="n">
+        <v>4.008551576697162e-05</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.0001439722441399366</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.0005869039586144903</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.0003269987929966994</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>8.675602627331025e-05</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0.0001602564102564097</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.000164473684210531</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0.0007977463907285099</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.0004674716317888378</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0.0006588446673614579</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0.0003595956761668046</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.0002712132470236772</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0.001629373432553541</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.0006010257780701383</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.0002478518347786118</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.0001170851229611331</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.0005820834144289939</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.0003519093130497808</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>8.22368421052655e-05</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0.0001105108055009935</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
         <v>8.017103153394324e-05</v>
       </c>
-      <c r="BP8" t="n">
-        <v>0.0003085152712751171</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>0.0004396114944404866</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>0.0004592381824524427</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>7.367387033397065e-05</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>0.0002735799895778962</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0.001161966040373316</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0.0007781980731574351</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>0.0003721737019439008</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>0.0008477788705843758</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>0.0001977907924335193</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>0.0002109168006093703</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>0.0003580820611104457</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>0.0001202565473009398</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>0.0002496796934454232</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>0.0001053199847018127</v>
-      </c>
       <c r="CP8" t="n">
         <v>0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0008241758241757962</v>
+        <v>0.000406636974858765</v>
       </c>
       <c r="CR8" t="n">
-        <v>-2.672367717797552e-05</v>
+        <v>3.683693516699782e-05</v>
       </c>
       <c r="CS8" t="n">
-        <v>-8.326672684688674e-18</v>
+        <v>0.0001105108055009851</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.68369351669895e-05</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>3.957783641160839e-05</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0002872675824727305</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0001167466700575326</v>
+        <v>0.0007986354967087966</v>
       </c>
       <c r="CZ8" t="n">
         <v>0</v>
       </c>
       <c r="DA8" t="n">
-        <v>7.84929356357794e-05</v>
+        <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0003271643546803538</v>
+        <v>8.017103153394324e-05</v>
       </c>
       <c r="DC8" t="n">
-        <v>4.008551576697162e-05</v>
+        <v>0.0003605769230769218</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>9.355317659961726e-05</v>
+        <v>5.236449415597644e-05</v>
       </c>
       <c r="DF8" t="n">
-        <v>9.0361445783127e-05</v>
+        <v>0.0003343902664866505</v>
       </c>
       <c r="DG8" t="n">
-        <v>0</v>
+        <v>0.0008302715734628402</v>
       </c>
       <c r="DH8" t="n">
-        <v>1.665334536937735e-17</v>
+        <v>0.0007672857814165296</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0004118459900745719</v>
+        <v>0.0003986785318207897</v>
       </c>
       <c r="DJ8" t="n">
         <v>0</v>
       </c>
       <c r="DK8" t="n">
-        <v>0</v>
+        <v>3.683693516699782e-05</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>4.518072289157182e-05</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>0.0003968904821783248</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.000156331422615949</v>
+        <v>0.001063010822879496</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0004966338477262493</v>
+        <v>0.0004886258989708709</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
@@ -4387,10 +4387,10 @@
         <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>8.291873963515718e-05</v>
+        <v>0.0009326487005058447</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>0.0005947855753045989</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4399,22 +4399,22 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0</v>
+        <v>0.0001841846758349891</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0001569858712715755</v>
+        <v>0.000329564631504714</v>
       </c>
       <c r="DZ8" t="n">
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0</v>
+        <v>9.797898059901445e-05</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0001517903901544909</v>
+        <v>0.001242137071907243</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0009989644606684029</v>
+        <v>0.0006431458857807965</v>
       </c>
       <c r="ED8" t="n">
         <v>0</v>
@@ -4435,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>8.017103153394324e-05</v>
+        <v>3.92464678179022e-05</v>
       </c>
       <c r="EK8" t="n">
         <v>0</v>
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>3.683693516699782e-05</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
@@ -4468,7 +4468,7 @@
         <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>4.518072289157182e-05</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001644736842105288</v>
+        <v>0.004657247514390372</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.0009086050240513233</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00030120481927709</v>
+        <v>0.001370614035087714</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0007849293563578996</v>
+        <v>0.001602564102564097</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0007326007326007078</v>
+        <v>0.0003837719298245723</v>
       </c>
       <c r="G9" t="n">
-        <v>5.211047420531356e-05</v>
+        <v>0.002190170940170932</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001229289150187096</v>
+        <v>0.006698063840920987</v>
       </c>
       <c r="I9" t="n">
+        <v>0.001864035087719262</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002850877192982426</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0002137894174238486</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001602564102564097</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0001964636542239884</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.00392464678178962</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.002831325301204846</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0004819277108434217</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.004447933019361583</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.004761904761904768</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.00245944531658816</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.0006385068762279067</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.001831501831501825</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.002302631578947323</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.003506017791732052</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.00748262960983429</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.0007849293563579219</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.0009900990099009576</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.003674698795180753</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.0007849293563579219</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.001771756122980661</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.0128205128205128</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.01935166994106093</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.0009823182711198642</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.000694444444444442</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.002616431187859736</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.002302631578947323</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.01006024096385546</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.02135007849293564</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.001096491228070207</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.004604918890633147</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.002891566265060264</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.007749866381614101</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.000328947368421062</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.003313253012048212</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.01124754420432223</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.002028508771929782</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.001388888888888884</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.001315789473684204</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.0004273504273504258</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.003044871794871784</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.0002136752136752129</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.002657634184471025</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.001831501831501825</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.00181623931623931</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.01449502878074305</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.000164473684210531</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.0007675438596491446</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.0006802721088435271</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.007430664573521706</v>
+      </c>
+      <c r="BG9" t="n">
         <v>0.001175213675213671</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.000497512437810943</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.0001658374792703143</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0004216867469879259</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.0005402750491158903</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.001335470085470081</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.003035060177917282</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.002357563850687616</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.01036878674505618</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.001602564102564097</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.001875977071391399</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.00151753008895863</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.003580972741849298</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.001014957264957261</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.002701375245579563</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.004810261892036394</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>5.232862375719183e-05</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.0003869541182974001</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.0004709576138147376</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.00267236771779803</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.007910208444682033</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.02156188605108054</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.005255402750491145</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.001549145299145294</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.001326129666011733</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.0009942438513866781</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.01021611001964635</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.03025120256547304</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0.0004273504273504258</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.008017103153393944</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.001024096385542162</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.00673436664885092</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.0004273504273504258</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.0009615384615384581</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.01301571709233791</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.006227106227106216</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.0009081196581196549</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.001726844583987408</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.001412872841444257</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.001014957264957261</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0.0002616431187859591</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0.001098901098901051</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.000261643118785948</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0.003367183324425482</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0.003855421686746985</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0.0005402750491158903</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0.0007849293563578774</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.001602564102564097</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0.01177394034536888</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0.002564102564102511</v>
-      </c>
       <c r="BH9" t="n">
-        <v>0.000240963855421672</v>
+        <v>0.0006802721088435271</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.003804064616988068</v>
+        <v>0.01271585557299841</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.002350427350427342</v>
+        <v>0.004081632653061218</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.001098901098901073</v>
+        <v>0.002993051843933703</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.000120481927710836</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.000497512437810943</v>
+        <v>0.001098901098901117</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.004275788348476783</v>
+        <v>0.001973684210526283</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.001831501831501814</v>
+        <v>0.003585461689587488</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0008970976253297902</v>
+        <v>0.0004934210526315929</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.002308447937131619</v>
+        <v>0.00347407803313734</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.002111984282907631</v>
+        <v>0.001375245579567808</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.004543025120256605</v>
+        <v>0.001603420630678765</v>
       </c>
       <c r="BU9" t="n">
+        <v>0.0005482456140351033</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.0006385068762279067</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.0001068947087119243</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.001425438596491191</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.001831501831501825</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.007430664573521717</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.000785854616895898</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.0008223684210526327</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.001315789473684215</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.00219780219780219</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.005756148613291457</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.0009823182711198642</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.000982318271119853</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.002354788069073765</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.001375245579567785</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.000694444444444442</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.0005344735435596215</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.0003438113948919464</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.003035060177917315</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.0004911591355599376</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.004552590266875978</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.0004807692307692291</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.0003837719298245723</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>9.823182711199419e-05</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.0002455795677799855</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.0002137894174238375</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.0003929273084479545</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.0016559829059829</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.0004385964912280827</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.0001563314226159407</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0.0006876227897839038</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.0005756148613291657</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>5.344735435595105e-05</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.0005876068376068355</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.001068376068376065</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.002982731554160101</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.004440789473684204</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.003924646781789642</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.0001068376068376065</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.0005211047420531356</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0.001122394441475116</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.0005732152162584492</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.003508771929824539</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.001918859649122773</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.0001096491228070207</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.000602409638554291</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>5.344735435596215e-05</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.001443078567610867</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.002825745682888536</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.0003012048192771455</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.0007295466388743899</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.001535087719298212</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.0003438113948919574</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.00367324561403507</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.002564102564102555</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.0002946954813359603</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0.0009419152276295307</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.0009900990099009576</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.000694444444444442</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.00090860502405129</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.0003206841261357729</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>6.02409638554291e-05</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0.0002137894174238486</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0.0005756148613291434</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ9" t="n">
         <v>0.0002136752136752129</v>
       </c>
-      <c r="BV9" t="n">
-        <v>0.0002605523710265789</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0.0005421686746987841</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0.001976495726495719</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0.001522593320235721</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.003527525387493347</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0.003438113948919441</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0.002405130946018208</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0.001277013752455769</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>0.0005876068376068355</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>0.0006860158311345454</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>0.0005402750491158681</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>0.001098901098901062</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>0.001031434184675795</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>5.277044854881119e-05</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>0.0005876068376068355</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>0.0009081196581196549</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>0.0007326007326006855</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>0.0003693931398416783</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0.000343811394891913</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>0.00149572649572649</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>0.001175213675213671</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>0.0008547008547008517</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>0.000374131480491735</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>0.0008895866038722611</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX9" t="n">
-        <v>0.001308215593929851</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>0.0005732152162584936</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>0.0003929273084478879</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>0.0007858546168958202</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>0.002040816326530603</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>0.0001068947087119354</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>0.0003869541182974001</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>0.0004221635883904895</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>0.001068376068376065</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>0.0005876068376068355</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0.002210216110019636</v>
-      </c>
-      <c r="DJ9" t="n">
+      <c r="ER9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.0001068947087119243</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0.0003438113948919685</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0.0001602564102564097</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0.0003663003663003761</v>
+      </c>
+      <c r="EY9" t="n">
         <v>0.0003206841261357729</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>0.000694444444444442</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>9.823182711197199e-05</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>5.344735435596215e-05</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>0.0007367387033398454</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>0.001015499732763281</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>5.277044854881119e-05</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>5.232862375718072e-05</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0.000120481927710836</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>0.00160342063067882</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0.0005527915975677145</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>0.0001068947087119243</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>5.341880341880323e-05</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>0.001228632478632474</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA9" t="n">
-        <v>0.0004221635883904895</v>
-      </c>
-      <c r="EB9" t="n">
-        <v>0.001080550098231803</v>
-      </c>
-      <c r="EC9" t="n">
-        <v>0.00181728880157167</v>
-      </c>
-      <c r="ED9" t="n">
-        <v>0.000196463654223944</v>
-      </c>
-      <c r="EE9" t="n">
-        <v>0.0001603420630678864</v>
-      </c>
-      <c r="EF9" t="n">
-        <v>0.0003739316239316226</v>
-      </c>
-      <c r="EG9" t="n">
-        <v>0.001571709233791696</v>
-      </c>
-      <c r="EH9" t="n">
-        <v>0.0006279434850863019</v>
-      </c>
-      <c r="EI9" t="n">
-        <v>0.0002616431187859369</v>
-      </c>
-      <c r="EJ9" t="n">
-        <v>0.0005341880341880323</v>
-      </c>
-      <c r="EK9" t="n">
-        <v>0.0004807692307692291</v>
-      </c>
-      <c r="EL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM9" t="n">
-        <v>4.911591355598599e-05</v>
-      </c>
-      <c r="EN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP9" t="n">
-        <v>0.001015499732763281</v>
-      </c>
-      <c r="EQ9" t="n">
-        <v>0.0007858546168958425</v>
-      </c>
-      <c r="ER9" t="n">
-        <v>0</v>
-      </c>
-      <c r="ES9" t="n">
-        <v>0.0001068947087119243</v>
-      </c>
-      <c r="ET9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EU9" t="n">
-        <v>0.0005876068376068355</v>
-      </c>
-      <c r="EV9" t="n">
-        <v>0.000196463654223944</v>
-      </c>
-      <c r="EW9" t="n">
-        <v>0.0005341880341880323</v>
-      </c>
-      <c r="EX9" t="n">
-        <v>0.000694444444444442</v>
-      </c>
-      <c r="EY9" t="n">
-        <v>4.911591355598599e-05</v>
       </c>
     </row>
   </sheetData>
